--- a/Example/TableManagerUnity/Assets/Excels/DataItem.xlsx
+++ b/Example/TableManagerUnity/Assets/Excels/DataItem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\TableManager\Example\TableManagerUnity\Assets\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\unity-data-table\Example\TableManagerUnity\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B41701-38DF-42BA-8315-02657D82D658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FCA032-7F6E-49D8-9A1C-B61C29451CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataItem" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>string</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -416,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="B1:D6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -424,63 +420,60 @@
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="C4" s="2">
         <v>123</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2">
         <v>2300</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2">
         <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
